--- a/output/pdf_financials_xlsx/TORR.xlsx
+++ b/output/pdf_financials_xlsx/TORR.xlsx
@@ -5982,22 +5982,22 @@
         <v>1.211413</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.243764</v>
+        <v>1.413449</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.160876</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.186761</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.270192</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.303912</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.303912</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>2.303912</v>
@@ -7447,13 +7447,13 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>2.295205</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>0.348346</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>0.03372</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -16167,7 +16167,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -17240,7 +17244,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -19389,7 +19397,11 @@
           <t>Reserves 2,270,192</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -21724,7 +21736,11 @@
           <t>Reserves 2,160,876 1,725,814</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -34608,7 +34624,11 @@
           <t>Write-down of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -35487,7 +35507,11 @@
           <t>Write-down of exploration and evaluation expenditures (Note 6(i))</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -36784,7 +36808,11 @@
           <t>Writedown of exploration and evaluation expenditures (Note 6(i))</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TORR.xlsx
+++ b/output/pdf_financials_xlsx/TORR.xlsx
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.036158</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009093</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001939</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005388</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.008554000000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.09052499999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.390661</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.153843</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.08391899999999999</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.017543</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.003695</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.029479</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.04926</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.06519800000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2059,34 +2059,34 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.427875</v>
+        <v>-1.391717</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.814672</v>
+        <v>-0.823765</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.748561</v>
+        <v>1.746622</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.8743</v>
+        <v>-0.879688</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.08656</v>
+        <v>-0.095114</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.246454</v>
+        <v>-1.336979</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.0644</v>
+        <v>-0.326261</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.377681</v>
+        <v>-0.531524</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.006266</v>
+        <v>-0.090185</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.994783</v>
+        <v>0.97724</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>2.701734</v>
@@ -2100,16 +2100,16 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-7.570149</v>
+        <v>-7.573844</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.74905</v>
+        <v>-6.778529</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.651381</v>
+        <v>4.602121</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>4.628048</v>
+        <v>4.56285</v>
       </c>
     </row>
     <row r="28">
@@ -2179,34 +2179,34 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.427875</v>
+        <v>-1.391717</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.814672</v>
+        <v>-0.823765</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.754357</v>
+        <v>1.752418</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.8699</v>
+        <v>-0.875288</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.08343399999999999</v>
+        <v>-0.091988</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.245942</v>
+        <v>-1.336467</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.064707</v>
+        <v>-0.325954</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.377681</v>
+        <v>-0.531524</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.006266</v>
+        <v>-0.090185</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.994783</v>
+        <v>0.97724</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>2.701734</v>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-7.570149</v>
+        <v>-7.573844</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.74905</v>
+        <v>-6.778529</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>4.651381</v>
+        <v>4.602121</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>4.628048</v>
+        <v>4.56285</v>
       </c>
     </row>
     <row r="30">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-7.466723864679035</v>
+        <v>-107.466723864679</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>54.02612284798784</v>
+        <v>53.07337207407809</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>0.469297</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>5.57365</v>
+        <v>0.469297</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>6.958134</v>
@@ -2604,7 +2604,7 @@
         <v>0.469297</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>5.52365</v>
+        <v>0.419297</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>6.958134</v>
@@ -3300,7 +3300,7 @@
         <v>2.914903</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0</v>
+        <v>2.964903</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.042652</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -40030,7 +40030,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -42667,7 +42667,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -45156,7 +45156,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -49479,7 +49479,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -52798,7 +52798,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -54020,7 +54020,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -55226,7 +55226,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -56444,7 +56444,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -60490,7 +60490,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E521" s="5" t="n">

--- a/output/pdf_financials_xlsx/TORR.xlsx
+++ b/output/pdf_financials_xlsx/TORR.xlsx
@@ -786,19 +786,19 @@
         <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.032688</v>
+        <v>0.098065</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.033141</v>
+        <v>0.086641</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.05259</v>
+        <v>0.101545</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.059224</v>
+        <v>0.118578</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.102479</v>
+        <v>0.180178</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.168822</v>
+        <v>0.289572</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.131514</v>
+        <v>0.250014</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.103478</v>
+        <v>0.221978</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.120354</v>
+        <v>0.238854</v>
       </c>
     </row>
     <row r="8">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.032688</v>
+        <v>0.098065</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.410185</v>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.032688</v>
+        <v>-0.098065</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.326266</v>
@@ -7029,13 +7029,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00585</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000445</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01621</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7236,22 +7236,22 @@
         <v>-10.934908</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-8.657278</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-11.822583</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-4.371816</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0</v>
+        <v>-2.250282</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>-7.562496</v>
       </c>
       <c r="R114" s="3" t="n">
-        <v>0</v>
+        <v>-20.179951</v>
       </c>
     </row>
     <row r="115">
@@ -7291,25 +7291,25 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>11.013333</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>9.440785</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>12.131808</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>5.140749</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>3.254404</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>9.649295</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>10.860368</v>
       </c>
     </row>
     <row r="116">
@@ -8431,13 +8431,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00585</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000445</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01621</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.548099</v>
+        <v>-0.5643089999999999</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.431207</v>
@@ -26352,7 +26352,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -26441,7 +26445,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -37818,7 +37826,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E295" s="5" t="n">
         <v>-0.00585</v>
       </c>
@@ -40539,7 +40551,11 @@
           <t>Directors’ fees (note 9)</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -43071,7 +43087,11 @@
           <t>Directors’ fees (note 8)</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -46661,7 +46681,11 @@
           <t>Directors fees (note 8)</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -50087,7 +50111,11 @@
           <t>Directors fees (note 10)</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -52202,7 +52230,11 @@
           <t>Directors fees (note 9)</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
